--- a/data/trans_bre/IP21B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 82,23</t>
+          <t>-37,6; 82,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 23,76</t>
+          <t>-38,25; 23,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 33,01</t>
+          <t>-40,66; 29,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 78,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,24</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 85,27</t>
+          <t>-39,94; 85,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 55,68</t>
+          <t>-73,85; 55,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 74,89</t>
+          <t>-50,21; 74,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 0,0</t>
+          <t>-51,98; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 28,71</t>
+          <t>-51,1; 25,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,49</t>
+          <t>0,0; 53,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-53,84; 79,59</t>
+          <t>-52,73; 87,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 61,65</t>
+          <t>-25,64; 58,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 53,5</t>
+          <t>-41,62; 41,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 68,31</t>
+          <t>-15,15; 70,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 9,7</t>
+          <t>-14,51; 11,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 12,03</t>
+          <t>-16,32; 14,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 22,2</t>
+          <t>-20,79; 21,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 31,78</t>
+          <t>-30,15; 32,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 201,84</t>
+          <t>-86,28; 214,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-74,76; 121,5</t>
+          <t>-73,48; 163,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 263,39</t>
+          <t>-63,61; 216,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-94,78; 337,47</t>
+          <t>-82,54; 492,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Provincia-trans_bre.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 82,4</t>
+          <t>-38,39; 82,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 23,57</t>
+          <t>-38,39; 23,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 29,15</t>
+          <t>-37,99; 32,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,91</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 85,17</t>
+          <t>-34,72; 84,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,85; 55,68</t>
+          <t>-80,06; 55,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 74,95</t>
+          <t>-50,21; 74,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 0,0</t>
+          <t>-59,27; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 25,23</t>
+          <t>-50,56; 30,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,33</t>
+          <t>0,0; 48,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 87,08</t>
+          <t>-53,17; 79,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 58,77</t>
+          <t>-25,92; 61,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 41,44</t>
+          <t>-40,98; 42,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 70,67</t>
+          <t>-23,55; 70,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 11,02</t>
+          <t>-15,24; 10,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 14,84</t>
+          <t>-18,34; 13,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 21,02</t>
+          <t>-20,5; 20,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 32,53</t>
+          <t>-33,12; 29,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-86,28; 214,12</t>
+          <t>-84,24; 212,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 163,44</t>
+          <t>-74,33; 143,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-63,61; 216,21</t>
+          <t>-63,23; 187,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 492,8</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-53,27</t>
+          <t>-50,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 82,0</t>
+          <t>-38,53; 82,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38,24</t>
+          <t>38,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 23,66</t>
+          <t>-38,12; 23,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 32,75</t>
+          <t>-40,3; 33,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,73</t>
+          <t>32,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 75,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 84,23</t>
+          <t>-34,72; 85,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,06; 55,68</t>
+          <t>-72,13; 55,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,42</t>
+          <t>25,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 0,0</t>
+          <t>-51,62; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 30,65</t>
+          <t>-43,59; 28,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,33</t>
+          <t>0,0; 49,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 79,59</t>
+          <t>-49,21; 82,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 61,66</t>
+          <t>-26,03; 61,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 42,05</t>
+          <t>-35,53; 53,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 70,57</t>
+          <t>-23,03; 68,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 10,26</t>
+          <t>-15,7; 9,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 13,43</t>
+          <t>-16,98; 12,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 20,86</t>
+          <t>-20,88; 22,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 29,51</t>
+          <t>-32,09; 34,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-84,24; 212,71</t>
+          <t>-84,34; 201,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 143,92</t>
+          <t>-74,76; 121,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 187,57</t>
+          <t>-64,46; 263,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,54</t>
         </is>
       </c>
     </row>
